--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
@@ -555,7 +555,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="B13">

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
@@ -1,46 +1,197 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Cobertura_Comunal" sheetId="1" r:id="rId1"/>
+    <sheet name="Cobertura_Comunal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cobertura_Comunal'!$A$1:$D$31</definedName>
+  </definedNames>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+  <si>
+    <t xml:space="preserve">comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proyectada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaitén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Montt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puqueldón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calbuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chonchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quellón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Muermos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llanquihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queilén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Octay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maullín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochamó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Varas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Juan de la Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frutillar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futaleufú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pablo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualaihué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puyehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27 21:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00135A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,21 +199,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -112,10 +279,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -141,15 +304,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -175,6 +335,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,513 +511,524 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>comuna</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Residentes</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Proyectada</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Cobertura</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Chaitén</t>
-        </is>
-      </c>
-      <c r="B2">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>4954</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2" t="n">
         <v>5078</v>
       </c>
-      <c r="D2">
-        <v>97.558093737692</v>
+      <c r="D2" s="2" t="n">
+        <v>97.56</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="B3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>280415</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2" t="n">
         <v>280955</v>
       </c>
-      <c r="D3">
-        <v>99.8077984018793</v>
+      <c r="D3" s="2" t="n">
+        <v>99.81</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Puqueldón</t>
-        </is>
-      </c>
-      <c r="B4">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>4183</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2" t="n">
         <v>4188</v>
       </c>
-      <c r="D4">
-        <v>99.88061127029609</v>
+      <c r="D4" s="2" t="n">
+        <v>99.88</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Osorno</t>
-        </is>
-      </c>
-      <c r="B5">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>177260</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2" t="n">
         <v>176304</v>
       </c>
-      <c r="D5">
-        <v>100.5422452128142</v>
+      <c r="D5" s="2" t="n">
+        <v>100.54</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Curaco de Vélez</t>
-        </is>
-      </c>
-      <c r="B6">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>4192</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2" t="n">
         <v>4135</v>
       </c>
-      <c r="D6">
-        <v>101.3784764207981</v>
+      <c r="D6" s="2" t="n">
+        <v>101.38</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Purranque</t>
-        </is>
-      </c>
-      <c r="B7">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>21316</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2" t="n">
         <v>20968</v>
       </c>
-      <c r="D7">
-        <v>101.6596718809615</v>
+      <c r="D7" s="2" t="n">
+        <v>101.66</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Calbuco</t>
-        </is>
-      </c>
-      <c r="B8">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>38781</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2" t="n">
         <v>37626</v>
       </c>
-      <c r="D8">
-        <v>103.0696858555254</v>
+      <c r="D8" s="2" t="n">
+        <v>103.07</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Quinchao</t>
-        </is>
-      </c>
-      <c r="B9">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>8484</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2" t="n">
         <v>8186</v>
       </c>
-      <c r="D9">
-        <v>103.6403615929636</v>
+      <c r="D9" s="2" t="n">
+        <v>103.64</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Quemchi</t>
-        </is>
-      </c>
-      <c r="B10">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>9269</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2" t="n">
         <v>8754</v>
       </c>
-      <c r="D10">
-        <v>105.8830249029015</v>
+      <c r="D10" s="2" t="n">
+        <v>105.88</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chonchi</t>
-        </is>
-      </c>
-      <c r="B11">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="n">
         <v>17412</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2" t="n">
         <v>16267</v>
       </c>
-      <c r="D11">
-        <v>107.0387901887256</v>
+      <c r="D11" s="2" t="n">
+        <v>107.04</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Quellón</t>
-        </is>
-      </c>
-      <c r="B12">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="n">
         <v>32260</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2" t="n">
         <v>30136</v>
       </c>
-      <c r="D12">
-        <v>107.0480488452349</v>
+      <c r="D12" s="2" t="n">
+        <v>107.05</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Los Muermos</t>
-        </is>
-      </c>
-      <c r="B13">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="n">
         <v>19319</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2" t="n">
         <v>17832</v>
       </c>
-      <c r="D13">
-        <v>108.3389412292508</v>
+      <c r="D13" s="2" t="n">
+        <v>108.34</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fresia</t>
-        </is>
-      </c>
-      <c r="B14">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="n">
         <v>13691</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2" t="n">
         <v>12571</v>
       </c>
-      <c r="D14">
-        <v>108.9093946384536</v>
+      <c r="D14" s="2" t="n">
+        <v>108.91</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Llanquihue</t>
-        </is>
-      </c>
-      <c r="B15">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="n">
         <v>20623</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2" t="n">
         <v>18863</v>
       </c>
-      <c r="D15">
-        <v>109.3304352435986</v>
+      <c r="D15" s="2" t="n">
+        <v>109.33</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Queilén</t>
-        </is>
-      </c>
-      <c r="B16">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="n">
         <v>6124</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2" t="n">
         <v>5542</v>
       </c>
-      <c r="D16">
-        <v>110.5016239624684</v>
+      <c r="D16" s="2" t="n">
+        <v>110.5</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Puerto Octay</t>
-        </is>
-      </c>
-      <c r="B17">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="n">
         <v>10107</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2" t="n">
         <v>9056</v>
       </c>
-      <c r="D17">
-        <v>111.6055653710247</v>
+      <c r="D17" s="2" t="n">
+        <v>111.61</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Castro</t>
-        </is>
-      </c>
-      <c r="B18">
+      <c r="A18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2" t="n">
         <v>54451</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2" t="n">
         <v>48727</v>
       </c>
-      <c r="D18">
-        <v>111.747080673959</v>
+      <c r="D18" s="2" t="n">
+        <v>111.75</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Dalcahue</t>
-        </is>
-      </c>
-      <c r="B19">
+      <c r="A19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="2" t="n">
         <v>17302</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2" t="n">
         <v>15456</v>
       </c>
-      <c r="D19">
-        <v>111.9435817805383</v>
+      <c r="D19" s="2" t="n">
+        <v>111.94</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Ancud</t>
-        </is>
-      </c>
-      <c r="B20">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2" t="n">
         <v>47900</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2" t="n">
         <v>42524</v>
       </c>
-      <c r="D20">
-        <v>112.6422725990029</v>
+      <c r="D20" s="2" t="n">
+        <v>112.64</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Maullín</t>
-        </is>
-      </c>
-      <c r="B21">
+      <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="n">
         <v>16739</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2" t="n">
         <v>14735</v>
       </c>
-      <c r="D21">
-        <v>113.6002714625042</v>
+      <c r="D21" s="2" t="n">
+        <v>113.6</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Cochamó</t>
-        </is>
-      </c>
-      <c r="B22">
+      <c r="A22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="2" t="n">
         <v>4526</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2" t="n">
         <v>3947</v>
       </c>
-      <c r="D22">
-        <v>114.6693691411198</v>
+      <c r="D22" s="2" t="n">
+        <v>114.67</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Puerto Varas</t>
-        </is>
-      </c>
-      <c r="B23">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="n">
         <v>59399</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2" t="n">
         <v>51316</v>
       </c>
-      <c r="D23">
-        <v>115.7514225582664</v>
+      <c r="D23" s="2" t="n">
+        <v>115.75</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>San Juan de la Costa</t>
-        </is>
-      </c>
-      <c r="B24">
+      <c r="A24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="2" t="n">
         <v>8608</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2" t="n">
         <v>7424</v>
       </c>
-      <c r="D24">
-        <v>115.948275862069</v>
+      <c r="D24" s="2" t="n">
+        <v>115.95</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Río Negro</t>
-        </is>
-      </c>
-      <c r="B25">
+      <c r="A25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="2" t="n">
         <v>16459</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2" t="n">
         <v>14085</v>
       </c>
-      <c r="D25">
-        <v>116.8548100816471</v>
+      <c r="D25" s="2" t="n">
+        <v>116.85</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Frutillar</t>
-        </is>
-      </c>
-      <c r="B26">
+      <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2" t="n">
         <v>24731</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2" t="n">
         <v>20817</v>
       </c>
-      <c r="D26">
-        <v>118.8019407215257</v>
+      <c r="D26" s="2" t="n">
+        <v>118.8</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Futaleufú</t>
-        </is>
-      </c>
-      <c r="B27">
+      <c r="A27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="2" t="n">
         <v>3492</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2" t="n">
         <v>2912</v>
       </c>
-      <c r="D27">
-        <v>119.9175824175824</v>
+      <c r="D27" s="2" t="n">
+        <v>119.92</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>San Pablo</t>
-        </is>
-      </c>
-      <c r="B28">
+      <c r="A28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>13258</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2" t="n">
         <v>10537</v>
       </c>
-      <c r="D28">
-        <v>125.8232893612983</v>
+      <c r="D28" s="2" t="n">
+        <v>125.82</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Hualaihué</t>
-        </is>
-      </c>
-      <c r="B29">
+      <c r="A29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>12083</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2" t="n">
         <v>9586</v>
       </c>
-      <c r="D29">
-        <v>126.0484039223868</v>
+      <c r="D29" s="2" t="n">
+        <v>126.05</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Puyehue</t>
-        </is>
-      </c>
-      <c r="B30">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2" t="n">
         <v>15164</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2" t="n">
         <v>11818</v>
       </c>
-      <c r="D30">
-        <v>128.3127432729734</v>
+      <c r="D30" s="2" t="n">
+        <v>128.31</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Palena</t>
-        </is>
-      </c>
-      <c r="B31">
+      <c r="A31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="2" t="n">
         <v>2497</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2" t="n">
         <v>1826</v>
       </c>
-      <c r="D31">
-        <v>136.7469879518072</v>
+      <c r="D31" s="2" t="n">
+        <v>136.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D31"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">comuna</t>
   </si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:15</t>
+    <t xml:space="preserve">2026-08-07 07:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -141,16 +141,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_comunal_cobertura_2024_los_lagos.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura de residentes (comunal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Los Lagos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
   </si>
 </sst>
 </file>
@@ -1008,23 +1017,23 @@
         <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:13</t>
+    <t xml:space="preserve">2026-08-28 11:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:14</t>
+    <t xml:space="preserve">2026-09-01 13:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 13:23</t>
+    <t xml:space="preserve">2026-09-06 17:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:20</t>
+    <t xml:space="preserve">2026-09-08 13:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
